--- a/src/sm/decodetable.xlsx
+++ b/src/sm/decodetable.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC276"/>
+  <dimension ref="A1:AC277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,12 +554,12 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>atomic</t>
         </is>
       </c>
     </row>
@@ -29530,7 +29530,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>VSUB_VV</t>
+          <t>VSUB12_VI</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -29570,7 +29570,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -29580,7 +29580,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -29590,7 +29590,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -29655,7 +29655,7 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
@@ -29677,7 +29677,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VSUB_VX</t>
+          <t>VSUB_VV</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -29732,7 +29732,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -29824,7 +29824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VXOR_VI</t>
+          <t>VSUB_VX</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -29879,12 +29879,12 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>FN_XOR</t>
+          <t>FN_SUB</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -29971,7 +29971,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VXOR_VV</t>
+          <t>VXOR_VI</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -30118,7 +30118,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>VXOR_VX</t>
+          <t>VXOR_VV</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -30260,22 +30260,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>VFPU</t>
+          <t>VALU</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FADD_S</t>
+          <t>VXOR_VX</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -30315,7 +30315,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -30335,7 +30335,7 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>FN_FADD</t>
+          <t>FN_XOR</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
@@ -30365,7 +30365,7 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
@@ -30380,7 +30380,7 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FCLASS_S</t>
+          <t>FADD_S</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -30462,7 +30462,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -30482,7 +30482,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>FN_FCLASS</t>
+          <t>FN_FADD</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FCVT_S_W</t>
+          <t>FCLASS_S</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>FN_I2F</t>
+          <t>FN_FCLASS</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -30706,7 +30706,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FCVT_S_WU</t>
+          <t>FCVT_S_W</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -30756,7 +30756,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>FN_IU2F</t>
+          <t>FN_I2F</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -30853,7 +30853,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FCVT_WU_S</t>
+          <t>FCVT_S_WU</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -30923,7 +30923,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>FN_F2IU</t>
+          <t>FN_IU2F</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
@@ -31000,7 +31000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FCVT_W_S</t>
+          <t>FCVT_WU_S</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -31050,7 +31050,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>FN_F2I</t>
+          <t>FN_F2IU</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FEQ_S</t>
+          <t>FCVT_W_S</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -31197,7 +31197,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -31217,7 +31217,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>FN_FEQ</t>
+          <t>FN_F2I</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -31294,7 +31294,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FLE_S</t>
+          <t>FEQ_S</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>FN_FLE</t>
+          <t>FN_FEQ</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -31441,7 +31441,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FLT_S</t>
+          <t>FLE_S</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -31511,7 +31511,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>FN_FLT</t>
+          <t>FN_FLE</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FMADD_S</t>
+          <t>FLT_S</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -31633,7 +31633,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>A3_FRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>FN_FMADD</t>
+          <t>FN_FLT</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FMAX_S</t>
+          <t>FMADD_S</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_FRS3</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>FN_FMAX</t>
+          <t>FN_FMADD</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -31882,7 +31882,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FMIN_S</t>
+          <t>FMAX_S</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>FN_FMIN</t>
+          <t>FN_FMAX</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FMSUB_S</t>
+          <t>FMIN_S</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>A3_FRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -32099,7 +32099,7 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>FN_FMSUB</t>
+          <t>FN_FMIN</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>FMUL_S</t>
+          <t>FMSUB_S</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -32221,7 +32221,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_FRS3</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -32246,7 +32246,7 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>FN_FMUL</t>
+          <t>FN_FMSUB</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -32323,7 +32323,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FNMADD_S</t>
+          <t>FMUL_S</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>A3_FRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -32393,7 +32393,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>FN_FNMADD</t>
+          <t>FN_FMUL</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>FNMSUB_S</t>
+          <t>FNMADD_S</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -32540,7 +32540,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>FN_FNMSUB</t>
+          <t>FN_FNMADD</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -32617,7 +32617,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FSGNJN_S</t>
+          <t>FNMSUB_S</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -32662,7 +32662,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_FRS3</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>FN_FSGNJN</t>
+          <t>FN_FNMSUB</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -32764,7 +32764,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>FSGNJX_S</t>
+          <t>FSGNJN_S</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -32834,7 +32834,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>FN_FSGNJX</t>
+          <t>FN_FSGNJN</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FSGNJ_S</t>
+          <t>FSGNJX_S</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -32981,7 +32981,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>FN_FSGNJ</t>
+          <t>FN_FSGNJX</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -33058,7 +33058,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FSUB_S</t>
+          <t>FSGNJ_S</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -33128,7 +33128,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>FN_FSUB</t>
+          <t>FN_FSGNJ</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -33205,12 +33205,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>VFADD_VF</t>
+          <t>FSUB_S</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -33255,7 +33255,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -33275,7 +33275,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>FN_FADD</t>
+          <t>FN_FSUB</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -33305,7 +33305,7 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
@@ -33320,7 +33320,7 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
@@ -33352,7 +33352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>VFADD_VV</t>
+          <t>VFADD_VF</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -33407,7 +33407,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -33499,7 +33499,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>VFCLASS_V</t>
+          <t>VFADD_VV</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>FN_FCLASS</t>
+          <t>FN_FADD</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>VFCVT_F_XU_V</t>
+          <t>VFCLASS_V</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -33716,7 +33716,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>FN_IU2F</t>
+          <t>FN_FCLASS</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>VFCVT_F_X_V</t>
+          <t>VFCVT_F_XU_V</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>FN_I2F</t>
+          <t>FN_IU2F</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>VFCVT_RTZ_XU_F_V</t>
+          <t>VFCVT_F_X_V</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -34010,7 +34010,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>FN_F2IU</t>
+          <t>FN_I2F</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -34087,7 +34087,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>VFCVT_RTZ_X_F_V</t>
+          <t>VFCVT_RTZ_XU_F_V</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>FN_F2I</t>
+          <t>FN_F2IU</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -34234,7 +34234,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>VFCVT_XU_F_V</t>
+          <t>VFCVT_RTZ_X_F_V</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -34304,7 +34304,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>FN_F2IU</t>
+          <t>FN_F2I</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -34381,7 +34381,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>VFCVT_X_F_V</t>
+          <t>VFCVT_XU_F_V</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>FN_F2I</t>
+          <t>FN_F2IU</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
@@ -34528,7 +34528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>VFMACC_VF</t>
+          <t>VFCVT_X_F_V</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -34573,7 +34573,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -34583,7 +34583,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>FN_FMADD</t>
+          <t>FN_F2I</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -34675,7 +34675,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>VFMACC_VV</t>
+          <t>VFMACC_VF</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -34730,7 +34730,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -34822,7 +34822,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>VFMADD_VF</t>
+          <t>VFMACC_VV</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -34862,7 +34862,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>FN_VFMADD</t>
+          <t>FN_FMADD</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>VFMADD_VV</t>
+          <t>VFMADD_VF</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>VFMAX_VF</t>
+          <t>VFMADD_VV</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -35161,7 +35161,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -35171,7 +35171,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -35186,7 +35186,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>FN_FMAX</t>
+          <t>FN_VFMADD</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>VFMAX_VV</t>
+          <t>VFMAX_VF</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -35410,7 +35410,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>VFMIN_VF</t>
+          <t>VFMAX_VV</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -35465,7 +35465,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -35480,7 +35480,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>FN_FMIN</t>
+          <t>FN_FMAX</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -35557,7 +35557,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>VFMIN_VV</t>
+          <t>VFMIN_VF</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -35612,7 +35612,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -35704,7 +35704,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>VFMSAC_VF</t>
+          <t>VFMIN_VV</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -35744,12 +35744,12 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -35759,7 +35759,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -35774,7 +35774,7 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>FN_FMSUB</t>
+          <t>FN_FMIN</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>VFMSAC_VV</t>
+          <t>VFMSAC_VF</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>VFMSUB_VF</t>
+          <t>VFMSAC_VV</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -36038,7 +36038,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -36053,7 +36053,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -36068,7 +36068,7 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>FN_VFMSUB</t>
+          <t>FN_FMSUB</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
@@ -36145,7 +36145,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>VFMSUB_VV</t>
+          <t>VFMSUB_VF</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -36200,7 +36200,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -36292,7 +36292,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>VFMUL_VF</t>
+          <t>VFMSUB_VV</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -36347,7 +36347,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -36362,7 +36362,7 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>FN_FMUL</t>
+          <t>FN_VFMSUB</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
@@ -36439,7 +36439,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>VFMUL_VV</t>
+          <t>VFMUL_VF</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -36494,7 +36494,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -36586,7 +36586,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>VFNMACC_VF</t>
+          <t>VFMUL_VV</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -36641,7 +36641,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -36656,7 +36656,7 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>FN_FNMADD</t>
+          <t>FN_FMUL</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
@@ -36733,7 +36733,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>VFNMACC_VV</t>
+          <t>VFNMACC_VF</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -36880,7 +36880,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>VFNMADD_VF</t>
+          <t>VFNMACC_VV</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -36920,7 +36920,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -36935,7 +36935,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -36950,7 +36950,7 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>FN_VFNMADD</t>
+          <t>FN_FNMADD</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>VFNMADD_VV</t>
+          <t>VFNMADD_VF</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -37082,7 +37082,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -37174,7 +37174,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>VFNMSAC_VF</t>
+          <t>VFNMADD_VV</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -37214,7 +37214,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -37229,7 +37229,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -37244,7 +37244,7 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>FN_FNMSUB</t>
+          <t>FN_VFNMADD</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
@@ -37321,7 +37321,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>VFNMSAC_VV</t>
+          <t>VFNMSAC_VF</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -37376,7 +37376,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>VFNMSUB_VF</t>
+          <t>VFNMSAC_VV</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -37508,7 +37508,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -37538,7 +37538,7 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>FN_VFNMSUB</t>
+          <t>FN_FNMSUB</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
@@ -37615,7 +37615,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>VFNMSUB_VV</t>
+          <t>VFNMSUB_VF</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -37670,7 +37670,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -37762,7 +37762,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>VFRSUB_VF</t>
+          <t>VFNMSUB_VV</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -37807,7 +37807,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>FN_FSUB</t>
+          <t>FN_VFNMSUB</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
@@ -37909,7 +37909,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>VFSGNJN_VF</t>
+          <t>VFRSUB_VF</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -37949,7 +37949,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -37979,7 +37979,7 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>FN_FSGNJN</t>
+          <t>FN_FSUB</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>VFSGNJN_VV</t>
+          <t>VFSGNJN_VF</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -38111,7 +38111,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>VFSGNJX_VF</t>
+          <t>VFSGNJN_VV</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -38273,7 +38273,7 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>FN_FSGNJX</t>
+          <t>FN_FSGNJN</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -38350,7 +38350,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>VFSGNJX_VV</t>
+          <t>VFSGNJX_VF</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -38405,7 +38405,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>VFSGNJ_VF</t>
+          <t>VFSGNJX_VV</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -38567,7 +38567,7 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>FN_FSGNJ</t>
+          <t>FN_FSGNJX</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
@@ -38644,7 +38644,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>VFSGNJ_VV</t>
+          <t>VFSGNJ_VF</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -38699,7 +38699,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -38791,7 +38791,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>VFSUB_VF</t>
+          <t>VFSGNJ_VV</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -38846,7 +38846,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>FN_FSUB</t>
+          <t>FN_FSGNJ</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
@@ -38938,7 +38938,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>VFSUB_VV</t>
+          <t>VFSUB_VF</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -38993,7 +38993,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -39085,7 +39085,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>VMFEQ_VF</t>
+          <t>VFSUB_VV</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -39125,7 +39125,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -39155,7 +39155,7 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>FN_FEQ</t>
+          <t>FN_FSUB</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>VMFEQ_VV</t>
+          <t>VMFEQ_VF</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -39287,7 +39287,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -39379,7 +39379,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>VMFGE_VF</t>
+          <t>VMFEQ_VV</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -39434,7 +39434,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -39449,7 +39449,7 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>FN_FLE</t>
+          <t>FN_FEQ</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
@@ -39526,7 +39526,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>VMFGT_VF</t>
+          <t>VMFGE_VF</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -39596,7 +39596,7 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>FN_FLT</t>
+          <t>FN_FLE</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
@@ -39673,7 +39673,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>VMFLE_VF</t>
+          <t>VMFGT_VF</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -39743,7 +39743,7 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>FN_FLE</t>
+          <t>FN_FLT</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
@@ -39820,7 +39820,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>VMFLE_VV</t>
+          <t>VMFLE_VF</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>VMFLT_VF</t>
+          <t>VMFLE_VV</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -40037,7 +40037,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>FN_FLT</t>
+          <t>FN_FLE</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
@@ -40114,7 +40114,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>VMFLT_VV</t>
+          <t>VMFLT_VF</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -40169,7 +40169,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -40261,7 +40261,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>VMFNE_VF</t>
+          <t>VMFLT_VV</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -40301,7 +40301,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -40331,7 +40331,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>FN_FNE</t>
+          <t>FN_FLT</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
@@ -40408,7 +40408,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>VMFNE_VV</t>
+          <t>VMFNE_VF</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -40463,7 +40463,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -40550,27 +40550,27 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>WPSCHEDLER</t>
+          <t>VFPU</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>BARRIER</t>
+          <t>VMFNE_VV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -40605,17 +40605,17 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>IMM_Z</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_FNE</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
@@ -40655,7 +40655,7 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W274" t="inlineStr">
@@ -40702,7 +40702,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>BARRIERSUB</t>
+          <t>BARRIER</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -40849,140 +40849,287 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
+          <t>BARRIERSUB</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>B_N</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>CSR_N</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>A3_X</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>A2_X</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>A1_IMM</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>IMM_Z</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>MEM_X</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>FN_ADD</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>M_X</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>WPSCHEDLER</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
           <t>ENDPRG</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
         <is>
           <t>B_N</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
         <is>
           <t>CSR_N</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
         <is>
           <t>A3_X</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
+      <c r="L277" t="inlineStr">
         <is>
           <t>A2_X</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr">
+      <c r="M277" t="inlineStr">
         <is>
           <t>A1_X</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr">
+      <c r="N277" t="inlineStr">
         <is>
           <t>IMM_X</t>
         </is>
       </c>
-      <c r="O276" t="inlineStr">
+      <c r="O277" t="inlineStr">
         <is>
           <t>MEM_X</t>
         </is>
       </c>
-      <c r="P276" t="inlineStr">
+      <c r="P277" t="inlineStr">
         <is>
           <t>FN_ADD</t>
         </is>
       </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R276" t="inlineStr">
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
         <is>
           <t>M_X</t>
         </is>
       </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/src/sm/decodetable.xlsx
+++ b/src/sm/decodetable.xlsx
@@ -24308,7 +24308,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>FN_SLTU</t>
+          <t>FN_SLT</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>FN_SLTU</t>
+          <t>FN_SLT</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">

--- a/src/sm/decodetable.xlsx
+++ b/src/sm/decodetable.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC277"/>
+  <dimension ref="A1:AC278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSRRW</t>
+          <t>CSRRSV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CSR_W</t>
+          <t>CSR_S</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CSRRWI</t>
+          <t>CSRRW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>IMM_Z</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SETRPC</t>
+          <t>CSRRWI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1503,17 +1503,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_Z</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VSETIVLI</t>
+          <t>SETRPC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CSR_S</t>
+          <t>CSR_W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1650,17 +1650,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>IMM_Z</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VSETVL</t>
+          <t>VSETIVLI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1797,17 +1797,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_Z</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VSETVLI</t>
+          <t>VSETVL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2036,17 +2036,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMOADD_W</t>
+          <t>VSETVLI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CSR_N</t>
+          <t>CSR_S</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_X</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>FN_AMOADD</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>M_XWR</t>
+          <t>M_X</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMOAND_W</t>
+          <t>AMOADD_W</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>FN_AND</t>
+          <t>FN_AMOADD</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMOMAXU_W</t>
+          <t>AMOAND_W</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>FN_MAXU</t>
+          <t>FN_AND</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMOMAX_W</t>
+          <t>AMOMAXU_W</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>FN_MAX</t>
+          <t>FN_MAXU</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMOMINU_W</t>
+          <t>AMOMAX_W</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>FN_MINU</t>
+          <t>FN_MAX</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMOMIN_W</t>
+          <t>AMOMINU_W</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>FN_MIN</t>
+          <t>FN_MINU</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMOOR_W</t>
+          <t>AMOMIN_W</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>FN_OR</t>
+          <t>FN_MIN</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMOSWAP_W</t>
+          <t>AMOOR_W</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>FN_SWAP</t>
+          <t>FN_OR</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMOXOR_W</t>
+          <t>AMOSWAP_W</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>FN_XOR</t>
+          <t>FN_SWAP</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>AMOXOR_W</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3424,17 +3424,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>MEM_B</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_XOR</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>M_XRD</t>
+          <t>M_XWR</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LBU</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>LBU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>MEM_H</t>
+          <t>MEM_B</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LHU</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LR_W</t>
+          <t>LHU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_H</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>LR_W</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A3_SD</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IMM_S</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>MEM_B</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>M_XWR</t>
+          <t>M_XRD</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SC_W</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_SD</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_S</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_B</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>SC_W</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A3_SD</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>IMM_S</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>MEM_H</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_H</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VLB12_V</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_SD</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4889,22 +4889,22 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_S</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MEM_B</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>FN_VLS12</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>M_XRD</t>
+          <t>M_XWR</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VLBU12_V</t>
+          <t>VLB12_V</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VLBU_V</t>
+          <t>VLBU12_V</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>IMM_L11</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_VLS12</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VLB_V</t>
+          <t>VLBU_V</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VLE32_V</t>
+          <t>VLB_V</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5472,22 +5472,22 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_L11</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_B</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VLH12_V</t>
+          <t>VLE32_V</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5619,27 +5619,27 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>MEM_H</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>FN_VLS12</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VLHU12_V</t>
+          <t>VLH12_V</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VLHU_V</t>
+          <t>VLHU12_V</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>IMM_L11</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_VLS12</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VLH_V</t>
+          <t>VLHU_V</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VLOXEI32_V</t>
+          <t>VLH_V</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6207,22 +6207,22 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_L11</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_H</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VLSE32_V</t>
+          <t>VLOXEI32_V</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VLW12_V</t>
+          <t>VLSE32_V</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>FN_VLS12</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VLW_V</t>
+          <t>VLW12_V</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>IMM_L11</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_VLS12</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VSB12_V</t>
+          <t>VLW_V</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A3_SD</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>IMM_S</t>
+          <t>IMM_L11</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>MEM_B</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>FN_VLS12</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>M_XWR</t>
+          <t>M_XRD</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VSB_V</t>
+          <t>VSB12_V</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>IMM_S11</t>
+          <t>IMM_S</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_VLS12</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VSE32_V</t>
+          <t>VSB_V</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7089,22 +7089,22 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_S11</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_B</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VSH12_V</t>
+          <t>VSE32_V</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7236,27 +7236,27 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>IMM_S</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>MEM_H</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>FN_VLS12</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VSH_V</t>
+          <t>VSH12_V</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>IMM_S11</t>
+          <t>IMM_S</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_VLS12</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VSOXEI32_V</t>
+          <t>VSH_V</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7530,22 +7530,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_S11</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>MEM_W</t>
+          <t>MEM_H</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VSSE32_V</t>
+          <t>VSOXEI32_V</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VSW12_V</t>
+          <t>VSSE32_V</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7824,17 +7824,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>IMM_S</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>FN_VLS12</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VSW_V</t>
+          <t>VSW12_V</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>IMM_S11</t>
+          <t>IMM_S</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_VLS12</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8063,17 +8063,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MUL</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MUL</t>
+          <t>VSW_V</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8113,42 +8113,42 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_SD</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_S11</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>MEM_X</t>
+          <t>MEM_W</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>FN_MUL</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>M_X</t>
+          <t>M_XWR</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MULH</t>
+          <t>MUL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>FN_MULH</t>
+          <t>FN_MUL</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MULHSU</t>
+          <t>MULH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>FN_MULHSU</t>
+          <t>FN_MULH</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MULHU</t>
+          <t>MULHSU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>FN_MULHU</t>
+          <t>FN_MULHSU</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VMACC_VV</t>
+          <t>MULHU</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8696,22 +8696,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>FN_MACC</t>
+          <t>FN_MULHU</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VMACC_VX</t>
+          <t>VMACC_VV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VMADD_VV</t>
+          <t>VMACC_VX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>FN_MADD</t>
+          <t>FN_MACC</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VMADD_VX</t>
+          <t>VMADD_VV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VMULHSU_VV</t>
+          <t>VMADD_VX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>FN_MULHSU</t>
+          <t>FN_MADD</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VMULHSU_VX</t>
+          <t>VMULHSU_VV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VMULHU_VV</t>
+          <t>VMULHSU_VX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>FN_MULHU</t>
+          <t>FN_MULHSU</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VMULHU_VX</t>
+          <t>VMULHU_VV</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VMULH_VV</t>
+          <t>VMULHU_VX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>FN_MULH</t>
+          <t>FN_MULHU</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VMULH_VX</t>
+          <t>VMULH_VV</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VMUL_VV</t>
+          <t>VMULH_VX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>FN_MUL</t>
+          <t>FN_MULH</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VMUL_VX</t>
+          <t>VMUL_VV</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VNMSAC_VV</t>
+          <t>VMUL_VX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>FN_NMSAC</t>
+          <t>FN_MUL</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VNMSAC_VX</t>
+          <t>VNMSAC_VV</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VNMSUB_VV</t>
+          <t>VNMSAC_VX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>FN_NMSUB</t>
+          <t>FN_NMSAC</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VNMSUB_VX</t>
+          <t>VNMSUB_VV</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -11003,17 +11003,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SALU</t>
+          <t>MUL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>VNMSUB_VX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11048,17 +11048,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -11078,12 +11078,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_NMSUB</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ADDI</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>ADDI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>FN_AND</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ANDI</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AUIPC</t>
+          <t>ANDI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>A1_PC</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>IMM_U</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_AND</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BEQ</t>
+          <t>AUIPC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>B_B</t>
+          <t>B_N</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -11788,22 +11788,22 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A3_PC</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_PC</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>IMM_B</t>
+          <t>IMM_U</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>FN_SEQ</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BGE</t>
+          <t>BEQ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>FN_SGE</t>
+          <t>FN_SEQ</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BGEU</t>
+          <t>BGE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>FN_SGEU</t>
+          <t>FN_SGE</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BLT</t>
+          <t>BGEU</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>FN_SLT</t>
+          <t>FN_SGEU</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BLTU</t>
+          <t>BLT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>FN_SLTU</t>
+          <t>FN_SLT</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BNE</t>
+          <t>BLTU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>FN_SNE</t>
+          <t>FN_SLTU</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FENCE</t>
+          <t>BNE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>B_N</t>
+          <t>B_B</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_PC</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_B</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_SNE</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JAL</t>
+          <t>FENCE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>B_J</t>
+          <t>B_N</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -12817,22 +12817,22 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>A3_PC</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>A2_SIZE</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>A1_PC</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>IMM_J</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JALR</t>
+          <t>JAL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>B_R</t>
+          <t>B_J</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_J</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LUI</t>
+          <t>JALR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>B_N</t>
+          <t>B_R</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -13111,22 +13111,22 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_PC</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_SIZE</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_PC</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>IMM_U</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>FN_A1ZERO</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>LUI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -13263,17 +13263,17 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_U</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>FN_OR</t>
+          <t>FN_A1ZERO</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ORI</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>ORI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>FN_SL</t>
+          <t>FN_OR</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SLLI</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>IMM_2</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SLT</t>
+          <t>SLLI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_2</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>FN_SLT</t>
+          <t>FN_SL</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SLTI</t>
+          <t>SLT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SLTIU</t>
+          <t>SLTI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>FN_SLTU</t>
+          <t>FN_SLT</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SLTU</t>
+          <t>SLTIU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SRA</t>
+          <t>SLTU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>FN_SRA</t>
+          <t>FN_SLTU</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SRAI</t>
+          <t>SRA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>IMM_2</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SRL</t>
+          <t>SRAI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_2</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>FN_SR</t>
+          <t>FN_SRA</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SRLI</t>
+          <t>SRL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>IMM_2</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SUB</t>
+          <t>SRLI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_2</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>FN_SUB</t>
+          <t>FN_SR</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>XOR</t>
+          <t>SUB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>FN_XOR</t>
+          <t>FN_SUB</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>XORI</t>
+          <t>XOR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -15413,12 +15413,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SFU</t>
+          <t>SALU</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>XORI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>FN_DIV</t>
+          <t>FN_XOR</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DIVU</t>
+          <t>DIV</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>FN_DIVU</t>
+          <t>FN_DIV</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FDIV_S</t>
+          <t>DIVU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>FN_FDIV</t>
+          <t>FN_DIVU</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FSQRT_S</t>
+          <t>FDIV_S</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>FN_FSQRT</t>
+          <t>FN_FDIV</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>REM</t>
+          <t>FSQRT_S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>FN_REM</t>
+          <t>FN_FSQRT</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>REMU</t>
+          <t>REM</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>FN_REMU</t>
+          <t>FN_REM</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -16300,12 +16300,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VDIVU_VV</t>
+          <t>REMU</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -16350,12 +16350,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>FN_DIVU</t>
+          <t>FN_REMU</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VDIVU_VX</t>
+          <t>VDIVU_VV</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VDIV_VV</t>
+          <t>VDIVU_VX</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>FN_DIV</t>
+          <t>FN_DIVU</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VDIV_VX</t>
+          <t>VDIV_VV</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VFDIV_VF</t>
+          <t>VDIV_VX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>FN_FDIV</t>
+          <t>FN_DIV</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VFDIV_VV</t>
+          <t>VFDIV_VF</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>VFEXP_V</t>
+          <t>VFDIV_VV</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>FN_EXP</t>
+          <t>FN_FDIV</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>VFRDIV_VF</t>
+          <t>VFEXP_V</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>FN_FDIV</t>
+          <t>FN_EXP</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VFSQRT_V</t>
+          <t>VFRDIV_VF</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>FN_FSQRT</t>
+          <t>FN_FDIV</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>VREMU_VV</t>
+          <t>VFSQRT_V</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -17693,7 +17693,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>FN_REMU</t>
+          <t>FN_FSQRT</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VREMU_VX</t>
+          <t>VREMU_VV</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VREM_VV</t>
+          <t>VREMU_VX</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>FN_REM</t>
+          <t>FN_REMU</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VREM_VX</t>
+          <t>VREM_VV</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -18206,12 +18206,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SIMTSTK</t>
+          <t>SFU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JOIN</t>
+          <t>VREM_VX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -18231,17 +18231,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>B_B</t>
+          <t>B_N</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -18251,27 +18251,27 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A3_PC</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>IMM_B</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_REM</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -18306,12 +18306,12 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
@@ -18353,12 +18353,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>SIMTSTK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>VFTTA_VV</t>
+          <t>JOIN</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -18378,17 +18378,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>B_N</t>
+          <t>B_B</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -18403,22 +18403,22 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_PC</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_B</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>FN_TTF</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
@@ -18500,12 +18500,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>TC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>VADD12_VI</t>
+          <t>VFTTA_VV</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -18545,17 +18545,17 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_TTF</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -18625,12 +18625,12 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VADD_VI</t>
+          <t>VADD12_VI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -18702,17 +18702,17 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VADD_VV</t>
+          <t>VADD_VI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -18854,12 +18854,12 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VADD_VX</t>
+          <t>VADD_VV</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VAND_VI</t>
+          <t>VADD_VX</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -19148,12 +19148,12 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -19163,7 +19163,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>FN_AND</t>
+          <t>FN_ADD</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VAND_VV</t>
+          <t>VAND_VI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VAND_VX</t>
+          <t>VAND_VV</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VBEQ</t>
+          <t>VAND_VX</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>B_B</t>
+          <t>B_N</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -19574,12 +19574,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A3_PC</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -19589,12 +19589,12 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>IMM_B</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>FN_SEQ</t>
+          <t>FN_AND</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
@@ -19681,7 +19681,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VBGE</t>
+          <t>VBEQ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>FN_SGE</t>
+          <t>FN_SEQ</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VBGEU</t>
+          <t>VBGE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>FN_SGEU</t>
+          <t>FN_SGE</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VBLT</t>
+          <t>VBGEU</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>FN_SLT</t>
+          <t>FN_SGEU</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VBLTU</t>
+          <t>VBLT</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>FN_SLTU</t>
+          <t>FN_SLT</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VBNE</t>
+          <t>VBLTU</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -20339,7 +20339,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>FN_SNE</t>
+          <t>FN_SLTU</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -20416,7 +20416,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VFMV_F_S</t>
+          <t>VBNE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20436,12 +20436,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>B_N</t>
+          <t>B_B</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -20456,12 +20456,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_PC</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -20471,12 +20471,12 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_B</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>FN_A1ZERO</t>
+          <t>FN_SNE</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VFMV_S_F</t>
+          <t>VFMV_F_S</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -20613,12 +20613,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>FN_A2ZERO</t>
+          <t>FN_A1ZERO</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VFMV_V_F</t>
+          <t>VFMV_S_F</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>VID_V</t>
+          <t>VFMV_V_F</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>FN_VID</t>
+          <t>FN_A2ZERO</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VMANDN_MM</t>
+          <t>VID_V</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>FN_VMANDNOT</t>
+          <t>FN_VID</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -21109,12 +21109,12 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VMAND_MM</t>
+          <t>VMANDN_MM</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>FN_AND</t>
+          <t>FN_VMANDNOT</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>VMAXU_VV</t>
+          <t>VMAND_MM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>FN_MAXU</t>
+          <t>FN_AND</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -21403,12 +21403,12 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -21445,7 +21445,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>VMAXU_VX</t>
+          <t>VMAXU_VV</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>VMAX_VV</t>
+          <t>VMAXU_VX</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>FN_MAX</t>
+          <t>FN_MAXU</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -21739,7 +21739,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>VMAX_VX</t>
+          <t>VMAX_VV</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>VMERGE_VIM</t>
+          <t>VMAX_VX</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -21941,12 +21941,12 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>FN_VMERGE</t>
+          <t>FN_MAX</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>VMERGE_VVM</t>
+          <t>VMERGE_VIM</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -22088,12 +22088,12 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>VMERGE_VXM</t>
+          <t>VMERGE_VVM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -22235,7 +22235,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>VMINU_VV</t>
+          <t>VMERGE_VXM</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>FN_MINU</t>
+          <t>FN_VMERGE</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>VMINU_VX</t>
+          <t>VMINU_VV</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>VMIN_VV</t>
+          <t>VMINU_VX</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>FN_MIN</t>
+          <t>FN_MINU</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>VMIN_VX</t>
+          <t>VMIN_VV</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -22823,7 +22823,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VMNAND_MM</t>
+          <t>VMIN_VX</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>FN_VMNAND</t>
+          <t>FN_MIN</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -23020,12 +23020,12 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -23062,7 +23062,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>VMNOR_MM</t>
+          <t>VMNAND_MM</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -23132,7 +23132,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>FN_VMNOR</t>
+          <t>FN_VMNAND</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>VMORN_MM</t>
+          <t>VMNOR_MM</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -23279,7 +23279,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>FN_VMORNOT</t>
+          <t>FN_VMNOR</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>VMOR_MM</t>
+          <t>VMORN_MM</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>FN_OR</t>
+          <t>FN_VMORNOT</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VMSEQ_VI</t>
+          <t>VMOR_MM</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -23558,12 +23558,12 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -23573,7 +23573,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>FN_SEQ</t>
+          <t>FN_OR</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -23608,12 +23608,12 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>VMSEQ_VV</t>
+          <t>VMSEQ_VI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -23705,12 +23705,12 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>VMSEQ_VX</t>
+          <t>VMSEQ_VV</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -23852,7 +23852,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>VMSGTU_VI</t>
+          <t>VMSEQ_VX</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -23999,12 +23999,12 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>IMM_Z</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>FN_SLTU</t>
+          <t>FN_SEQ</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -24054,7 +24054,7 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -24091,7 +24091,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>VMSGTU_VX</t>
+          <t>VMSGTU_VI</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_Z</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>VMSGT_VI</t>
+          <t>VMSGTU_VX</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -24293,12 +24293,12 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -24308,7 +24308,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>FN_SLT</t>
+          <t>FN_SLTU</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>VMSGT_VX</t>
+          <t>VMSGT_VI</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -24440,12 +24440,12 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -24532,7 +24532,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>VMSLEU_VI</t>
+          <t>VMSGT_VX</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -24587,12 +24587,12 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>IMM_Z</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>FN_SGEU</t>
+          <t>FN_SLT</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -24679,7 +24679,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>VMSLEU_VV</t>
+          <t>VMSLEU_VI</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -24734,12 +24734,12 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_Z</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -24826,7 +24826,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>VMSLEU_VX</t>
+          <t>VMSLEU_VV</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -24881,7 +24881,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>VMSLE_VI</t>
+          <t>VMSLEU_VX</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -25013,7 +25013,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>FN_SGE</t>
+          <t>FN_SGEU</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>VMSLE_VV</t>
+          <t>VMSLE_VI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -25175,12 +25175,12 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -25267,7 +25267,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>VMSLE_VX</t>
+          <t>VMSLE_VV</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -25322,7 +25322,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>VMSLTU_VV</t>
+          <t>VMSLE_VX</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -25454,7 +25454,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -25484,7 +25484,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>FN_SLTU</t>
+          <t>FN_SGE</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -25524,7 +25524,7 @@
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y171" t="inlineStr">
@@ -25561,7 +25561,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>VMSLTU_VX</t>
+          <t>VMSLTU_VV</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -25708,7 +25708,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>VMSLT_VV</t>
+          <t>VMSLTU_VX</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>FN_SLT</t>
+          <t>FN_SLTU</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>VMSLT_VX</t>
+          <t>VMSLT_VV</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -25910,7 +25910,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>VMSNE_VI</t>
+          <t>VMSLT_VX</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -26057,12 +26057,12 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>FN_SNE</t>
+          <t>FN_SLT</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>VMSNE_VV</t>
+          <t>VMSNE_VI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -26204,12 +26204,12 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>VMSNE_VX</t>
+          <t>VMSNE_VV</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -26351,7 +26351,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>VMV_S_X</t>
+          <t>VMSNE_VX</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -26513,7 +26513,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>FN_A2ZERO</t>
+          <t>FN_SNE</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -26590,7 +26590,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>VMV_V_I</t>
+          <t>VMV_S_X</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -26640,17 +26640,17 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>FN_A1ZERO</t>
+          <t>FN_A2ZERO</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>VMV_V_V</t>
+          <t>VMV_V_I</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -26787,17 +26787,17 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -26807,7 +26807,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>FN_A2ZERO</t>
+          <t>FN_A1ZERO</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -26884,7 +26884,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>VMV_V_X</t>
+          <t>VMV_V_V</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>VMV_X_S</t>
+          <t>VMV_V_X</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -27081,12 +27081,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>FN_A1ZERO</t>
+          <t>FN_A2ZERO</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
@@ -27178,7 +27178,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>VMXNOR_MM</t>
+          <t>VMV_X_S</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>FN_VMXNOR</t>
+          <t>FN_A1ZERO</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -27278,22 +27278,22 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>VMXOR_MM</t>
+          <t>VMXNOR_MM</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -27395,7 +27395,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>FN_XOR</t>
+          <t>FN_VMXNOR</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -27472,7 +27472,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>VOR_VI</t>
+          <t>VMXOR_MM</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>FN_OR</t>
+          <t>FN_XOR</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -27577,12 +27577,12 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>VOR_VV</t>
+          <t>VOR_VI</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -27674,12 +27674,12 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>VOR_VX</t>
+          <t>VOR_VV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -27913,7 +27913,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>VRSUB_VI</t>
+          <t>VOR_VX</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -27968,12 +27968,12 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>FN_SUB</t>
+          <t>FN_OR</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>VRSUB_VX</t>
+          <t>VRSUB_VI</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -28115,12 +28115,12 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>VSLL_VI</t>
+          <t>VRSUB_VX</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -28262,12 +28262,12 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>FN_SL</t>
+          <t>FN_SUB</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>VSLL_VV</t>
+          <t>VSLL_VI</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -28409,12 +28409,12 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -28501,7 +28501,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>VSLL_VX</t>
+          <t>VSLL_VV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -28648,7 +28648,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VSRA_VI</t>
+          <t>VSLL_VX</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -28703,12 +28703,12 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>FN_SRA</t>
+          <t>FN_SL</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -28795,7 +28795,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>VSRA_VV</t>
+          <t>VSRA_VI</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -28850,12 +28850,12 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -28942,7 +28942,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>VSRA_VX</t>
+          <t>VSRA_VV</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -28997,7 +28997,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>VSRL_VI</t>
+          <t>VSRA_VX</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -29144,12 +29144,12 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>FN_SR</t>
+          <t>FN_SRA</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -29236,7 +29236,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>VSRL_VV</t>
+          <t>VSRL_VI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -29383,7 +29383,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>VSRL_VX</t>
+          <t>VSRL_VV</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>VSUB12_VI</t>
+          <t>VSRL_VX</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -29570,7 +29570,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -29580,17 +29580,17 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>A2_IMM</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>IMM_I</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>FN_SUB</t>
+          <t>FN_SR</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
@@ -29655,7 +29655,7 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
@@ -29677,7 +29677,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VSUB_VV</t>
+          <t>VSUB12_VI</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_IMM</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -29737,7 +29737,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_I</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -29802,7 +29802,7 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
@@ -29824,7 +29824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VSUB_VX</t>
+          <t>VSUB_VV</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -29879,7 +29879,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -29971,7 +29971,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VXOR_VI</t>
+          <t>VSUB_VX</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>IMM_V</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -30041,7 +30041,7 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>FN_XOR</t>
+          <t>FN_SUB</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
@@ -30118,7 +30118,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>VXOR_VV</t>
+          <t>VXOR_VI</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -30173,12 +30173,12 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_IMM</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>IMM_X</t>
+          <t>IMM_V</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -30265,7 +30265,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>VXOR_VX</t>
+          <t>VXOR_VV</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -30407,22 +30407,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>VFPU</t>
+          <t>VALU</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FADD_S</t>
+          <t>VXOR_VX</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -30462,7 +30462,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -30482,7 +30482,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>FN_FADD</t>
+          <t>FN_XOR</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
@@ -30512,7 +30512,7 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FCLASS_S</t>
+          <t>FADD_S</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -30609,7 +30609,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>FN_FCLASS</t>
+          <t>FN_FADD</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -30706,7 +30706,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FCVT_S_W</t>
+          <t>FCLASS_S</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>FN_I2F</t>
+          <t>FN_FCLASS</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -30853,7 +30853,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FCVT_S_WU</t>
+          <t>FCVT_S_W</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -30903,7 +30903,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -30923,7 +30923,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>FN_IU2F</t>
+          <t>FN_I2F</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
@@ -31000,7 +31000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FCVT_WU_S</t>
+          <t>FCVT_S_WU</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>FN_F2IU</t>
+          <t>FN_IU2F</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FCVT_W_S</t>
+          <t>FCVT_WU_S</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -31197,7 +31197,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -31217,7 +31217,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>FN_F2I</t>
+          <t>FN_F2IU</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -31294,7 +31294,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FEQ_S</t>
+          <t>FCVT_W_S</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -31344,7 +31344,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>A2_RS2</t>
+          <t>A2_X</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>FN_FEQ</t>
+          <t>FN_F2I</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -31441,7 +31441,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FLE_S</t>
+          <t>FEQ_S</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -31511,7 +31511,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>FN_FLE</t>
+          <t>FN_FEQ</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FLT_S</t>
+          <t>FLE_S</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>FN_FLT</t>
+          <t>FN_FLE</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FMADD_S</t>
+          <t>FLT_S</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>A3_FRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>FN_FMADD</t>
+          <t>FN_FLT</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -31882,7 +31882,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FMAX_S</t>
+          <t>FMADD_S</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -31927,7 +31927,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_FRS3</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>FN_FMAX</t>
+          <t>FN_FMADD</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FMIN_S</t>
+          <t>FMAX_S</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -32099,7 +32099,7 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>FN_FMIN</t>
+          <t>FN_FMAX</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>FMSUB_S</t>
+          <t>FMIN_S</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -32221,7 +32221,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>A3_FRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -32246,7 +32246,7 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>FN_FMSUB</t>
+          <t>FN_FMIN</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -32323,7 +32323,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FMUL_S</t>
+          <t>FMSUB_S</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_FRS3</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -32393,7 +32393,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>FN_FMUL</t>
+          <t>FN_FMSUB</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>FNMADD_S</t>
+          <t>FMUL_S</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>A3_FRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -32540,7 +32540,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>FN_FNMADD</t>
+          <t>FN_FMUL</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -32617,7 +32617,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FNMSUB_S</t>
+          <t>FNMADD_S</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>FN_FNMSUB</t>
+          <t>FN_FNMADD</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -32764,7 +32764,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>FSGNJN_S</t>
+          <t>FNMSUB_S</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -32809,7 +32809,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_FRS3</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -32834,7 +32834,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>FN_FSGNJN</t>
+          <t>FN_FNMSUB</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FSGNJX_S</t>
+          <t>FSGNJN_S</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -32981,7 +32981,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>FN_FSGNJX</t>
+          <t>FN_FSGNJN</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -33058,7 +33058,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FSGNJ_S</t>
+          <t>FSGNJX_S</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -33128,7 +33128,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>FN_FSGNJ</t>
+          <t>FN_FSGNJX</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -33205,7 +33205,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>FSUB_S</t>
+          <t>FSGNJ_S</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -33275,7 +33275,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>FN_FSUB</t>
+          <t>FN_FSGNJ</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -33352,12 +33352,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>VFADD_VF</t>
+          <t>FSUB_S</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -33392,7 +33392,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -33402,7 +33402,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>A2_VRS2</t>
+          <t>A2_RS2</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -33422,7 +33422,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>FN_FADD</t>
+          <t>FN_FSUB</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -33452,7 +33452,7 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
@@ -33499,7 +33499,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>VFADD_VV</t>
+          <t>VFADD_VF</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>VFCLASS_V</t>
+          <t>VFADD_VV</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -33701,7 +33701,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>A1_X</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -33716,7 +33716,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>FN_FCLASS</t>
+          <t>FN_FADD</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>VFCVT_F_XU_V</t>
+          <t>VFCLASS_V</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>FN_IU2F</t>
+          <t>FN_FCLASS</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>VFCVT_F_X_V</t>
+          <t>VFCVT_F_XU_V</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -34010,7 +34010,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>FN_I2F</t>
+          <t>FN_IU2F</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -34087,7 +34087,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>VFCVT_RTZ_XU_F_V</t>
+          <t>VFCVT_F_X_V</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>FN_F2IU</t>
+          <t>FN_I2F</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -34234,7 +34234,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>VFCVT_RTZ_X_F_V</t>
+          <t>VFCVT_RTZ_XU_F_V</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -34304,7 +34304,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>FN_F2I</t>
+          <t>FN_F2IU</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -34381,7 +34381,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>VFCVT_XU_F_V</t>
+          <t>VFCVT_RTZ_X_F_V</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>FN_F2IU</t>
+          <t>FN_F2I</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
@@ -34528,7 +34528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>VFCVT_X_F_V</t>
+          <t>VFCVT_XU_F_V</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>FN_F2I</t>
+          <t>FN_F2IU</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -34675,7 +34675,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>VFMACC_VF</t>
+          <t>VFCVT_X_F_V</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -34730,7 +34730,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_X</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -34745,7 +34745,7 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>FN_FMADD</t>
+          <t>FN_F2I</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -34822,7 +34822,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>VFMACC_VV</t>
+          <t>VFMACC_VF</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>VFMADD_VF</t>
+          <t>VFMACC_VV</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -35009,7 +35009,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -35039,7 +35039,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>FN_VFMADD</t>
+          <t>FN_FMADD</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>VFMADD_VV</t>
+          <t>VFMADD_VF</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -35171,7 +35171,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>VFMAX_VF</t>
+          <t>VFMADD_VV</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -35308,7 +35308,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -35333,7 +35333,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>FN_FMAX</t>
+          <t>FN_VFMADD</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -35410,7 +35410,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>VFMAX_VV</t>
+          <t>VFMAX_VF</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -35465,7 +35465,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -35557,7 +35557,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>VFMIN_VF</t>
+          <t>VFMAX_VV</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -35612,7 +35612,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -35627,7 +35627,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>FN_FMIN</t>
+          <t>FN_FMAX</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -35704,7 +35704,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>VFMIN_VV</t>
+          <t>VFMIN_VF</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -35759,7 +35759,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>VFMSAC_VF</t>
+          <t>VFMIN_VV</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -35891,12 +35891,12 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>FN_FMSUB</t>
+          <t>FN_FMIN</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>VFMSAC_VV</t>
+          <t>VFMSAC_VF</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -36053,7 +36053,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -36145,7 +36145,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>VFMSUB_VF</t>
+          <t>VFMSAC_VV</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -36200,7 +36200,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -36215,7 +36215,7 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>FN_VFMSUB</t>
+          <t>FN_FMSUB</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
@@ -36292,7 +36292,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>VFMSUB_VV</t>
+          <t>VFMSUB_VF</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -36347,7 +36347,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -36439,7 +36439,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>VFMUL_VF</t>
+          <t>VFMSUB_VV</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -36484,7 +36484,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -36494,7 +36494,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>FN_FMUL</t>
+          <t>FN_VFMSUB</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
@@ -36586,7 +36586,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>VFMUL_VV</t>
+          <t>VFMUL_VF</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -36641,7 +36641,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -36733,7 +36733,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>VFNMACC_VF</t>
+          <t>VFMUL_VV</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -36773,12 +36773,12 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>A3_VRS3</t>
+          <t>A3_X</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>FN_FNMADD</t>
+          <t>FN_FMUL</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
@@ -36880,7 +36880,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>VFNMACC_VV</t>
+          <t>VFNMACC_VF</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -36935,7 +36935,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>VFNMADD_VF</t>
+          <t>VFNMACC_VV</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -37067,7 +37067,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -37082,7 +37082,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -37097,7 +37097,7 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>FN_VFNMADD</t>
+          <t>FN_FNMADD</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -37174,7 +37174,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>VFNMADD_VV</t>
+          <t>VFNMADD_VF</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -37229,7 +37229,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -37321,7 +37321,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>VFNMSAC_VF</t>
+          <t>VFNMADD_VV</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -37361,7 +37361,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -37376,7 +37376,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -37391,7 +37391,7 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>FN_FNMSUB</t>
+          <t>FN_VFNMADD</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>VFNMSAC_VV</t>
+          <t>VFNMSAC_VF</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -37615,7 +37615,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>VFNMSUB_VF</t>
+          <t>VFNMSAC_VV</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -37655,7 +37655,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -37670,7 +37670,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -37685,7 +37685,7 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>FN_VFNMSUB</t>
+          <t>FN_FNMSUB</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
@@ -37762,7 +37762,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>VFNMSUB_VV</t>
+          <t>VFNMSUB_VF</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -37909,7 +37909,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>VFRSUB_VF</t>
+          <t>VFNMSUB_VV</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -37954,7 +37954,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>A3_X</t>
+          <t>A3_VRS3</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -37964,7 +37964,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -37979,7 +37979,7 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>FN_FSUB</t>
+          <t>FN_VFNMSUB</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>VFSGNJN_VF</t>
+          <t>VFRSUB_VF</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -38096,7 +38096,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>FN_FSGNJN</t>
+          <t>FN_FSUB</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>VFSGNJN_VV</t>
+          <t>VFSGNJN_VF</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -38350,7 +38350,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>VFSGNJX_VF</t>
+          <t>VFSGNJN_VV</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -38405,7 +38405,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -38420,7 +38420,7 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>FN_FSGNJX</t>
+          <t>FN_FSGNJN</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>VFSGNJX_VV</t>
+          <t>VFSGNJX_VF</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -38644,7 +38644,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>VFSGNJ_VF</t>
+          <t>VFSGNJX_VV</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -38699,7 +38699,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -38714,7 +38714,7 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>FN_FSGNJ</t>
+          <t>FN_FSGNJX</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
@@ -38791,7 +38791,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>VFSGNJ_VV</t>
+          <t>VFSGNJ_VF</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -38846,7 +38846,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -38938,7 +38938,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>VFSUB_VF</t>
+          <t>VFSGNJ_VV</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -38993,7 +38993,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -39008,7 +39008,7 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>FN_FSUB</t>
+          <t>FN_FSGNJ</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
@@ -39085,7 +39085,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>VFSUB_VV</t>
+          <t>VFSUB_VF</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>VMFEQ_VF</t>
+          <t>VFSUB_VV</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -39272,7 +39272,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -39287,7 +39287,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -39302,7 +39302,7 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>FN_FEQ</t>
+          <t>FN_FSUB</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
@@ -39379,7 +39379,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>VMFEQ_VV</t>
+          <t>VMFEQ_VF</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -39434,7 +39434,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -39526,7 +39526,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>VMFGE_VF</t>
+          <t>VMFEQ_VV</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -39581,7 +39581,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -39596,7 +39596,7 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>FN_FLE</t>
+          <t>FN_FEQ</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
@@ -39673,7 +39673,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>VMFGT_VF</t>
+          <t>VMFGE_VF</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -39743,7 +39743,7 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>FN_FLT</t>
+          <t>FN_FLE</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
@@ -39820,7 +39820,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>VMFLE_VF</t>
+          <t>VMFGT_VF</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -39860,7 +39860,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -39890,7 +39890,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>FN_FLE</t>
+          <t>FN_FLT</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>VMFLE_VV</t>
+          <t>VMFLE_VF</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -40114,7 +40114,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>VMFLT_VF</t>
+          <t>VMFLE_VV</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -40169,7 +40169,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -40184,7 +40184,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>FN_FLT</t>
+          <t>FN_FLE</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
@@ -40261,7 +40261,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>VMFLT_VV</t>
+          <t>VMFLT_VF</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -40408,7 +40408,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>VMFNE_VF</t>
+          <t>VMFLT_VV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -40448,7 +40448,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -40463,7 +40463,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>A1_RS1</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>FN_FNE</t>
+          <t>FN_FLT</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
@@ -40555,7 +40555,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>VMFNE_VV</t>
+          <t>VMFNE_VF</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -40610,7 +40610,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>A1_VRS1</t>
+          <t>A1_RS1</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -40697,27 +40697,27 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>WPSCHEDLER</t>
+          <t>VFPU</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>BARRIER</t>
+          <t>VMFNE_VV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -40752,17 +40752,17 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>A2_X</t>
+          <t>A2_VRS2</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>A1_IMM</t>
+          <t>A1_VRS1</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>IMM_Z</t>
+          <t>IMM_X</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>FN_ADD</t>
+          <t>FN_FNE</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
@@ -40802,7 +40802,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>BARRIERSUB</t>
+          <t>BARRIER</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -40996,140 +40996,287 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
+          <t>BARRIERSUB</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>B_N</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>CSR_N</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>A3_X</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>A2_X</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>A1_IMM</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>IMM_Z</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>MEM_X</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>FN_ADD</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>M_X</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>WPSCHEDLER</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
           <t>ENDPRG</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
         <is>
           <t>B_N</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
         <is>
           <t>CSR_N</t>
         </is>
       </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
         <is>
           <t>A3_X</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
+      <c r="L278" t="inlineStr">
         <is>
           <t>A2_X</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr">
+      <c r="M278" t="inlineStr">
         <is>
           <t>A1_X</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr">
+      <c r="N278" t="inlineStr">
         <is>
           <t>IMM_X</t>
         </is>
       </c>
-      <c r="O277" t="inlineStr">
+      <c r="O278" t="inlineStr">
         <is>
           <t>MEM_X</t>
         </is>
       </c>
-      <c r="P277" t="inlineStr">
+      <c r="P278" t="inlineStr">
         <is>
           <t>FN_ADD</t>
         </is>
       </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R277" t="inlineStr">
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
         <is>
           <t>M_X</t>
         </is>
       </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/src/sm/decodetable.xlsx
+++ b/src/sm/decodetable.xlsx
@@ -17369,7 +17369,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
